--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484529_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484529_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>A. SEMEN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4507</v>
+        <v>1.1292</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8637</v>
+        <v>0.202</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.413</v>
+        <v>0.9273</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.6199</v>
+        <v>1.1292</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.7351</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.2988</v>
+        <v>0.3942</v>
       </c>
       <c r="J2" t="n">
-        <v>1.2213</v>
+        <v>1.082</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1796</v>
+        <v>1.0404</v>
       </c>
       <c r="L2" t="n">
         <v>0.0417</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.8412</v>
+        <v>0.0472</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5008</v>
+        <v>-0.3053</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.3404</v>
+        <v>0.3525</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.8326</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8326</v>
+        <v>0.733</v>
       </c>
       <c r="S2" t="n">
-        <v>4.6704</v>
+        <v>0.1833</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4412</v>
+        <v>0.0362</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2291</v>
+        <v>0.1471</v>
       </c>
       <c r="V2" t="n">
-        <v>2.2328</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8663</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SEMEN</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5139</v>
+        <v>0.7274</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5866</v>
+        <v>1.611</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9273</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1292</v>
+        <v>-1.6199</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7351</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3942</v>
+        <v>-2.2988</v>
       </c>
       <c r="J3" t="n">
-        <v>1.082</v>
+        <v>1.2213</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0404</v>
+        <v>1.1796</v>
       </c>
       <c r="L3" t="n">
         <v>0.0417</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0472</v>
+        <v>-2.8412</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3053</v>
+        <v>-0.5008</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3525</v>
+        <v>-2.3404</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1833</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R3" t="n">
-        <v>0.733</v>
+        <v>1.8326</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5679</v>
+        <v>1.947</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4208</v>
+        <v>1.1886</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1471</v>
+        <v>0.7585</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.2328</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.8663</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6569</v>
+        <v>0.2312</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5612</v>
+        <v>-0.9869</v>
       </c>
       <c r="F4" t="n">
         <v>1.2181</v>
@@ -766,10 +766,10 @@
         <v>2.1991</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5498</v>
+        <v>0.1241</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2911</v>
+        <v>-0.1346</v>
       </c>
       <c r="U4" t="n">
         <v>0.2586</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5171</v>
+        <v>-0.4209</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0334</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="F5" t="n">
         <v>-0.4837</v>
@@ -844,10 +844,10 @@
         <v>0.3665</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0551</v>
+        <v>0.0411</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0551</v>
+        <v>0.0411</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. JODAR SAIZ</t>
+          <t>J. CHALER ROMERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3722</v>
+        <v>-0.6627</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.999</v>
+        <v>-2.3117</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3732</v>
+        <v>1.649</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5623</v>
+        <v>-1.377</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.457</v>
+        <v>-0.7678</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0193</v>
+        <v>-0.6092</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7318</v>
+        <v>-0.5327</v>
       </c>
       <c r="K6" t="n">
-        <v>0.065</v>
+        <v>-0.5327</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6667999999999999</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1695</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.522</v>
+        <v>-0.2351</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3525</v>
+        <v>-0.6092</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9163</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9163</v>
+        <v>1.6493</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0732</v>
+        <v>0.2745</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2202</v>
+        <v>0.0536</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1471</v>
+        <v>0.221</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.945</v>
+        <v>0.6231</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.267</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CHALER ROMERO</t>
+          <t>J. JODAR SAIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6851</v>
+        <v>-1.276</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.136</v>
+        <v>-0.9029</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4508</v>
+        <v>-0.3732</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.377</v>
+        <v>0.5623</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7678</v>
+        <v>-0.457</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6092</v>
+        <v>1.0193</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5327</v>
+        <v>0.7318</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5327</v>
+        <v>0.065</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.1695</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2351</v>
+        <v>-0.522</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6092</v>
+        <v>0.3525</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1833</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6493</v>
+        <v>0.9163</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.748</v>
+        <v>0.023</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.1241</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0228</v>
+        <v>0.1471</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6231</v>
+        <v>-0.945</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6231</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9038</v>
+        <v>-2.0023</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6319</v>
+        <v>-1.9038</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2719</v>
+        <v>-0.0985</v>
       </c>
       <c r="G8" t="n">
         <v>-2.6342</v>
@@ -1078,13 +1078,13 @@
         <v>2.3823</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5262</v>
+        <v>0.3754</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.0426</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2446</v>
+        <v>0.418</v>
       </c>
       <c r="V8" t="n">
         <v>0.6231</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9763</v>
+        <v>-2.8772</v>
       </c>
       <c r="E9" t="n">
         <v>-1.8093</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.167</v>
+        <v>-1.0679</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1908</v>
@@ -1156,13 +1156,13 @@
         <v>0.733</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0078</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>0.2557</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2635</v>
+        <v>-0.1644</v>
       </c>
       <c r="V9" t="n">
         <v>0.3219</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3879</v>
+        <v>-3.9234</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.4335</v>
+        <v>-4.9939</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0457</v>
+        <v>1.0704</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9408</v>
@@ -1234,13 +1234,13 @@
         <v>2.5656</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2218</v>
+        <v>0.2426</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6252</v>
+        <v>-0.1855</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4034</v>
+        <v>0.4281</v>
       </c>
       <c r="V10" t="n">
         <v>0.6231</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3328</v>
+        <v>-4.6408</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.38</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.9528</v>
+        <v>-4.1263</v>
       </c>
       <c r="G11" t="n">
         <v>-4.2421</v>
@@ -1312,13 +1312,13 @@
         <v>2.0158</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5726</v>
+        <v>0.1193</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9909</v>
+        <v>-0.1255</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4183</v>
+        <v>0.2449</v>
       </c>
       <c r="V11" t="n">
         <v>-2.5339</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.3202</v>
+        <v>-7.3173</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6126</v>
+        <v>-3.7088</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7076</v>
+        <v>-3.6085</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5325</v>
@@ -1390,13 +1390,13 @@
         <v>1.8326</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1573</v>
+        <v>0.1603</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0905</v>
+        <v>-0.0056</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0668</v>
+        <v>0.1659</v>
       </c>
       <c r="V12" t="n">
         <v>-4.1125</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.5138</v>
+        <v>-8.079599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.2264</v>
+        <v>-5.8418</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2874</v>
+        <v>-2.2378</v>
       </c>
       <c r="G13" t="n">
         <v>-8.117599999999999</v>
@@ -1468,13 +1468,13 @@
         <v>1.0995</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9014</v>
+        <v>-0.4672</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7157</v>
+        <v>-0.3311</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1857</v>
+        <v>-0.1361</v>
       </c>
       <c r="V13" t="n">
         <v>0.3219</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-29.3877</v>
+        <v>-29.1124</v>
       </c>
       <c r="E14" t="n">
-        <v>-21.373</v>
+        <v>-21.0979</v>
       </c>
       <c r="F14" t="n">
         <v>-8.014699999999999</v>
@@ -1546,13 +1546,13 @@
         <v>18.3256</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8393</v>
+        <v>3.1147</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3507999999999993</v>
+        <v>0.6262000000000003</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4886</v>
+        <v>2.4887</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9449999999999996</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.7005</v>
+        <v>10.0881</v>
       </c>
       <c r="E15" t="n">
-        <v>8.753</v>
+        <v>9.041499999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9476</v>
+        <v>1.0466</v>
       </c>
       <c r="G15" t="n">
         <v>5.4384</v>
@@ -1624,13 +1624,13 @@
         <v>2.7489</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0885</v>
+        <v>-0.701</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6795</v>
+        <v>-0.391</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4091</v>
+        <v>-0.31</v>
       </c>
       <c r="V15" t="n">
         <v>4.4344</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.7728</v>
+        <v>7.0473</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3624</v>
+        <v>3.7855</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4104</v>
+        <v>3.2617</v>
       </c>
       <c r="G16" t="n">
         <v>2.1412</v>
@@ -1702,13 +1702,13 @@
         <v>2.7489</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9823</v>
+        <v>0.2568</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5664</v>
+        <v>-0.0105</v>
       </c>
       <c r="U16" t="n">
-        <v>0.416</v>
+        <v>0.2673</v>
       </c>
       <c r="V16" t="n">
         <v>1.9005</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.1258</v>
+        <v>3.9276</v>
       </c>
       <c r="E17" t="n">
         <v>2.182</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9439</v>
+        <v>1.7457</v>
       </c>
       <c r="G17" t="n">
         <v>5.056</v>
@@ -1780,13 +1780,13 @@
         <v>2.3823</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6929</v>
+        <v>0.4947</v>
       </c>
       <c r="T17" t="n">
         <v>0.0536</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6393</v>
+        <v>0.4412</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2566</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1564</v>
+        <v>2.9097</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3674</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>3.5238</v>
+        <v>3.7963</v>
       </c>
       <c r="G18" t="n">
         <v>3.2869</v>
@@ -1858,13 +1858,13 @@
         <v>3.1154</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.175</v>
+        <v>-0.4218</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7896</v>
+        <v>-0.3088</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3855</v>
+        <v>-0.113</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3219</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. MEDINA LERMA</t>
+          <t>A. SOLBES SORIANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0659</v>
+        <v>2.0983</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1351</v>
+        <v>-0.0027</v>
       </c>
       <c r="F19" t="n">
-        <v>3.201</v>
+        <v>2.101</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1098</v>
+        <v>1.2749</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6917</v>
+        <v>0.576</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8015</v>
+        <v>0.6989</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4195</v>
+        <v>1.0294</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1954</v>
+        <v>0.1701</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7759</v>
+        <v>0.8592</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5293</v>
+        <v>0.2456</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5036</v>
+        <v>0.4059</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0256</v>
+        <v>-0.1603</v>
       </c>
       <c r="P19" t="n">
         <v>1.6493</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6493</v>
+        <v>2.5656</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3713</v>
+        <v>-0.504</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7157</v>
+        <v>-0.1157</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3444</v>
+        <v>-0.3882</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3219</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SOLBES SORIANO</t>
+          <t>R. MEDINA LERMA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.922</v>
+        <v>2.0848</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0935</v>
+        <v>-0.9428</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8285</v>
+        <v>3.0276</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2749</v>
+        <v>1.1098</v>
       </c>
       <c r="H20" t="n">
-        <v>0.576</v>
+        <v>-0.6917</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6989</v>
+        <v>1.8015</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0294</v>
+        <v>-0.4195</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1701</v>
+        <v>-1.1954</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8592</v>
+        <v>0.7759</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2456</v>
+        <v>1.5293</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4059</v>
+        <v>0.5036</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1603</v>
+        <v>1.0256</v>
       </c>
       <c r="P20" t="n">
         <v>1.6493</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5656</v>
+        <v>1.6493</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6803</v>
+        <v>-0.3524</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0196</v>
+        <v>-0.5234</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6607</v>
+        <v>0.171</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3219</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4111</v>
+        <v>2.0435</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6531</v>
+        <v>-0.2685</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0642</v>
+        <v>2.312</v>
       </c>
       <c r="G21" t="n">
         <v>1.3719</v>
@@ -2092,13 +2092,13 @@
         <v>2.7489</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2277</v>
+        <v>-0.5954</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.3861</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.457</v>
+        <v>-0.2093</v>
       </c>
       <c r="V21" t="n">
         <v>1.267</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9213</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9292</v>
+        <v>1.1215</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.2308</v>
       </c>
       <c r="G22" t="n">
         <v>0.2546</v>
@@ -2170,13 +2170,13 @@
         <v>2.9321</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1109</v>
+        <v>-0.1416</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4223</v>
+        <v>-0.23</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3114</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3219</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.1668</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7242</v>
+        <v>-1.0127</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3033</v>
+        <v>1.1794</v>
       </c>
       <c r="G24" t="n">
         <v>-0.1633</v>
@@ -2326,13 +2326,13 @@
         <v>0.733</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3209</v>
+        <v>-0.0914</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3658</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0449</v>
+        <v>-0.1687</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3115</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0265</v>
+        <v>-0.259</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.1625</v>
+        <v>-2.5471</v>
       </c>
       <c r="F25" t="n">
-        <v>2.189</v>
+        <v>2.2881</v>
       </c>
       <c r="G25" t="n">
         <v>-0.9369</v>
@@ -2404,13 +2404,13 @@
         <v>1.4661</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1204</v>
+        <v>-0.1652</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1086</v>
+        <v>-0.276</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0118</v>
+        <v>0.1108</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6231</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S. CABRERA GONZALEZ</t>
+          <t>S. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7449</v>
+        <v>-0.957</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5706</v>
+        <v>-3.2665</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3155</v>
+        <v>2.3096</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1563</v>
+        <v>2.8168</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8181</v>
+        <v>2.095</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9744</v>
+        <v>0.7218</v>
       </c>
       <c r="J26" t="n">
-        <v>1.1763</v>
+        <v>1.9303</v>
       </c>
       <c r="K26" t="n">
-        <v>1.7339</v>
+        <v>1.8174</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5577</v>
+        <v>0.1129</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.3326</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.9157999999999999</v>
+        <v>0.2777</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.4167</v>
+        <v>0.6089</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3665</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.9163</v>
+        <v>-4.5814</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2828</v>
+        <v>3.1154</v>
       </c>
       <c r="S26" t="n">
-        <v>0.9454</v>
+        <v>-1.0304</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6222</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3232</v>
+        <v>-0.415</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.9005</v>
+        <v>-1.2774</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.5889</v>
+        <v>-1.2774</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S. CARRION BALLESTER</t>
+          <t>S. CABRERA GONZALEZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.174</v>
+        <v>-1.2781</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.4588</v>
+        <v>0.186</v>
       </c>
       <c r="F27" t="n">
-        <v>2.2848</v>
+        <v>-1.4641</v>
       </c>
       <c r="G27" t="n">
-        <v>2.8168</v>
+        <v>-0.1563</v>
       </c>
       <c r="H27" t="n">
-        <v>2.095</v>
+        <v>0.8181</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7218</v>
+        <v>-0.9744</v>
       </c>
       <c r="J27" t="n">
-        <v>1.9303</v>
+        <v>1.1763</v>
       </c>
       <c r="K27" t="n">
-        <v>1.8174</v>
+        <v>1.7339</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1129</v>
+        <v>-0.5577</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8866000000000001</v>
+        <v>-1.3326</v>
       </c>
       <c r="N27" t="n">
-        <v>0.2777</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>0.6089</v>
+        <v>-0.4167</v>
       </c>
       <c r="P27" t="n">
-        <v>-1.4661</v>
+        <v>0.3665</v>
       </c>
       <c r="Q27" t="n">
-        <v>-4.5814</v>
+        <v>-0.9163</v>
       </c>
       <c r="R27" t="n">
-        <v>3.1154</v>
+        <v>1.2828</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.2474</v>
+        <v>0.4121</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.8077</v>
+        <v>0.2376</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.4398</v>
+        <v>0.1746</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.2774</v>
+        <v>-1.9005</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.2774</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="28">
@@ -2593,10 +2593,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>29.3876</v>
+        <v>29.3877</v>
       </c>
       <c r="E28" t="n">
-        <v>8.014700000000003</v>
+        <v>8.014699999999998</v>
       </c>
       <c r="F28" t="n">
         <v>21.3731</v>
@@ -2623,13 +2623,13 @@
         <v>2.2114</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.03159999999999991</v>
+        <v>-0.03159999999999985</v>
       </c>
       <c r="O28" t="n">
         <v>2.243</v>
       </c>
       <c r="P28" t="n">
-        <v>9.162800000000001</v>
+        <v>9.162799999999999</v>
       </c>
       <c r="Q28" t="n">
         <v>-18.3259</v>
@@ -2638,13 +2638,13 @@
         <v>27.4887</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.8392</v>
+        <v>-2.8396</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.4885</v>
+        <v>-2.4884</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.3509000000000001</v>
+        <v>-0.3509</v>
       </c>
       <c r="V28" t="n">
         <v>0.9451999999999998</v>
